--- a/data/sample_7_answer.xlsx
+++ b/data/sample_7_answer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\port_React\portfolio_kweb\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\port_React _x\portfolio_kweb\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A15C43-AB3C-4F9E-B90C-315E2C775576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D5C7D2-EB0F-49C6-94DF-F8CFBA3C58CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9948" yWindow="1320" windowWidth="12984" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="解答" sheetId="1" r:id="rId1"/>
@@ -68,9 +68,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武</t>
+    <t>武豊</t>
     <rPh sb="0" eb="1">
       <t>タケ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ユタカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
